--- a/public/templates/bvb_financials_template.xlsx
+++ b/public/templates/bvb_financials_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BET-20" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BET-20" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -159,7 +159,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>BVB seed</author>
+    <author>CFO AI</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -755,34 +755,51 @@
       <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>BRD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>BRD-Groupe Société Générale</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
+      <c r="F3" s="3" t="n">
+        <v>6.3086</v>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -804,6 +821,15 @@
         <is>
           <t>Investment Fund</t>
         </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>2.1621</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.5582</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -852,7 +878,9 @@
       <c r="L5" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="M5" s="2" t="n"/>
+      <c r="M5" s="3" t="n">
+        <v>8.9194</v>
+      </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="3" t="n">
@@ -913,7 +941,9 @@
       <c r="L6" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M6" s="2" t="n"/>
+      <c r="M6" s="3" t="n">
+        <v>1.7123</v>
+      </c>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="3" t="n">
@@ -934,34 +964,59 @@
       <c r="U6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TGN</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Societatea Națională de Transport Gaze Naturale Transgaz S.A.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Gas Pipeline / Transport</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="n">
+        <v>2.2122</v>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>4.2788</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0.5547</v>
+      </c>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1035,13 +1090,17 @@
       <c r="L9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="M9" s="2" t="n"/>
+      <c r="M9" s="3" t="n">
+        <v>1.3776</v>
+      </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="Q9" s="2" t="n"/>
+      <c r="Q9" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="R9" s="3" t="n">
         <v>8</v>
       </c>
@@ -1056,34 +1115,59 @@
       <c r="U9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>SNN</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Societatea Națională Nuclearelectrica S.A.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Nuclear Power</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
+      <c r="F10" s="3" t="n">
+        <v>4.6805</v>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="3" t="n">
+        <v>1.7082</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>12.3432</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>1.6411</v>
+      </c>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1109,6 +1193,12 @@
       <c r="E11" s="4" t="n">
         <v>4.8</v>
       </c>
+      <c r="L11" s="4" t="n">
+        <v>4.0098</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.008</v>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>FY2024</t>
@@ -1116,34 +1206,59 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TEL</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Compania Națională de Transport al Energiei Electrice Transelectrica S.A.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Electricity Transmission</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
+      <c r="F12" s="3" t="n">
+        <v>7.6391</v>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="3" t="n">
+        <v>0.5859</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>5.815</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0.6716</v>
+      </c>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1216,7 +1331,9 @@
       <c r="L14" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="3" t="n">
+        <v>0.0153</v>
+      </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="3" t="n">
@@ -1233,34 +1350,59 @@
       <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ATB</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Antibiotice S.A.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Pharmaceuticals</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="3" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.8943</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1322,34 +1464,59 @@
       <c r="U16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>AQ</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Aquila Part Prod Com S.A.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>FMCG Distribution</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
+      <c r="F17" s="3" t="n">
+        <v>2.6403</v>
+      </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.5168</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1392,7 +1559,9 @@
       <c r="L18" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="3" t="n">
+        <v>0.0124</v>
+      </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="3" t="n">
@@ -1466,6 +1635,12 @@
       <c r="E20" s="4" t="n">
         <v>3.2</v>
       </c>
+      <c r="L20" s="4" t="n">
+        <v>1.4324</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0.1418</v>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>FY2024</t>
@@ -1473,30 +1648,2342 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>TRP</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Teraplast S.A.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Building Materials — PVC / Steel</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="F21" s="3" t="n">
+        <v>0.6424</v>
+      </c>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="3" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SSIF BRK Financial Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Brokerage</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EAI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Electro-Alfa International S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Electrical equipment</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Oil Terminal S.A.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Oil storage &amp; terminals</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="3" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="3" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ROC1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ROCA Industry HoldingRock1 S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Building-materials holding</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Impact Developer &amp; Contractor S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Residential development</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TRIP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Christian '76 Tour S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Travel &amp; tourism</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AROBS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AROBS Transilvania Software S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>COTE</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Conpet S.A.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Oil pipeline transport</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="3" t="n">
+        <v>0.5336</v>
+      </c>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="3" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.7307</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PBK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Patria Bank S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Altur S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Auto components</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SNO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Șantierul Naval Orșova S.A.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="3" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STZ.BVB</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sinteza S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CRC</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Chimcomplex S.A. Borzești</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>1.4955</v>
+      </c>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="3" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>2.0474</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>BVB</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Bursa de Valori București S.A.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Securities exchange</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="3" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="3" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Longshield Investment Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Investment holding</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Compa S.A.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Auto components</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="3" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="3" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TBK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Transilvania Broker de Asigurare S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Insurance brokerage</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Aerostar S.A.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; defense</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="3" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="3" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0.6203</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rompetrol Well Services S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Oilfield services</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lion Capital S.A.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Investment fund</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>IARV</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>IAR S.A. Brașov</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; defense</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="3" t="n">
+        <v>0.3816</v>
+      </c>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="3" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VNC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vrancart S.A.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Paper &amp; packaging</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RMAH</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Farmaceutica Remedia S.A.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pharma distribution</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EVER</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Evergent Investments S.A.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Investment fund</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.9824</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WINE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Purcari Wineries PLC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Wine &amp; spirits</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ENP</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Compania Energopetrol S.A.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Oilfield services</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BRM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Bermas S.A.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Brewing</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EFO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Turism, Hoteluri, Restaurante Marea Neagră S.A.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Hotels &amp; leisure</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SMTL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Simtel Team S.A.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Solar EPC &amp; engineering</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>COMI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Condmag S.A.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pipeline construction</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>BNET</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Bittnet Systems S.A.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>IT services</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="3" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="3" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
+      <c r="Q52" s="2" t="n"/>
+      <c r="R52" s="2" t="n"/>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TRANSI</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Transilvania Investments Alliance S.A.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Investment fund</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EBS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Erste Group Bank AG</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>BIO</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Biofarm S.A.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="3" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="3" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Safetech Innovations S.A.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AAG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AAGES S.A.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Electrical equipment</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ROCE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Romcarbon S.A.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plastics &amp; recycling</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RPH</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ropharma S.A.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pharmacy retail</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Rompetrol Rafinare S.A.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Refining &amp; marketing</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CMF</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Comelf S.A.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Metal structures &amp; machinery</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>INFINITY</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Infinity Capital Investments S.A.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Investment fund</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PREB</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Prebet Aiud S.A.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Concrete products</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ALR</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Alro S.A.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="3" t="n">
+        <v>3.4005</v>
+      </c>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="3" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.8819</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>0.6046</v>
+      </c>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
+      <c r="Q64" s="2" t="n"/>
+      <c r="R64" s="2" t="n"/>
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ALU</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Alumil Rom Industry S.A.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Aluminium systems</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UAM</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UAMT S.A.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Auto components</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>TBM</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Turbomecanica S.A.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Aero engines &amp; components</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="3" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n"/>
+      <c r="Q67" s="2" t="n"/>
+      <c r="R67" s="2" t="n"/>
+      <c r="S67" s="2" t="n"/>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CBC</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Carbochim S.A.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Abrasives</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="3" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="3" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="n"/>
+      <c r="Q68" s="2" t="n"/>
+      <c r="R68" s="2" t="n"/>
+      <c r="S68" s="2" t="n"/>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Green Tech International S.A.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plastics recycling</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CMCM</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>COMCM S.A. Constanța</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Construction materials</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BUCV</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Bucur S.A.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Wholesale &amp; distribution</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SOCP</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Socep S.A.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Port operations</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="3" t="n">
+        <v>0.2052</v>
+      </c>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="3" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="n"/>
+      <c r="Q72" s="2" t="n"/>
+      <c r="R72" s="2" t="n"/>
+      <c r="S72" s="2" t="n"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ELMA</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Electromagnetica S.A.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Electrical equipment</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="3" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="3" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>-7.58</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="n"/>
+      <c r="P73" s="2" t="n"/>
+      <c r="Q73" s="2" t="n"/>
+      <c r="R73" s="2" t="n"/>
+      <c r="S73" s="2" t="n"/>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ARM.BVB</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Armătura S.A.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Valves &amp; fittings</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BCM</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Casa de Bucovina-Club de Munte S.A.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Hotels &amp; leisure</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ECT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Grupul Industrial Electrocontact S.A.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Electrical components</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ELJ</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Electroaparataj S.A.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Electrical equipment</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ARTE</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Artego S.A.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Rubber products</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="3" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="3" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="n"/>
+      <c r="Q78" s="2" t="n"/>
+      <c r="R78" s="2" t="n"/>
+      <c r="S78" s="2" t="n"/>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>MECF</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Mecanica Ceahlău S.A.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Agricultural machinery</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="3" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="3" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>-27.1</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="n"/>
+      <c r="P79" s="2" t="n"/>
+      <c r="Q79" s="2" t="n"/>
+      <c r="R79" s="2" t="n"/>
+      <c r="S79" s="2" t="n"/>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 · ANAF</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ELGS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AETA S.A.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Household appliances</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CNTE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Conted S.A.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Apparel manufacturing</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MF Capital S.A.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Investment holding</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PPL</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Promateris S.A.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Bioplastics &amp; packaging</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PREH</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Prefab S.A.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Prefab concrete</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CAOR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SIF Hoteluri S.A.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Hotels &amp; leisure</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NAPO</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Societatea de Construcții Napoca S.A.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UZT</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Uztel S.A.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Oilfield equipment</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MCAB</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Romcab S.A.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Cables &amp; wiring</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VESY</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>VES S.A.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Household goods</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
@@ -1514,7 +4001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1681,7 +4168,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Why CFH is highlighted</t>
+          <t>Which rows matter most</t>
         </is>
       </c>
     </row>
@@ -1695,28 +4182,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cris-Tim Family Holding is Scandia Food's closest BVB-listed</t>
+          <t>A row that the Markets page shows in a peer comparison is read</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>peer (Romanian meat processor, comparable scale). The Markets</t>
+          <t>more often than any other. Check those rows first, and paste the</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>page leads with the CFH ↔ Scandia callout. Keeping CFH's row</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>accurate is higher leverage than any other BVB ticker.</t>
+          <t>source filing's URL for every figure you change.</t>
         </is>
       </c>
     </row>
